--- a/data/availability/projects/la-vista-developments/la-vista-gardens.xlsx
+++ b/data/availability/projects/la-vista-developments/la-vista-gardens.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Updated inventory for la-vista-gardens</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>

--- a/data/availability/projects/la-vista-developments/la-vista-gardens.xlsx
+++ b/data/availability/projects/la-vista-developments/la-vista-gardens.xlsx
@@ -797,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2028-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2029-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2028-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2028-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2028-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2029-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2029-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2029-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2029-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2029-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
